--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -1073,11 +1073,11 @@
         <v>116138308</v>
       </c>
       <c r="B5" t="n">
-        <v>83122</v>
+        <v>83042</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -808,14 +808,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108337157</v>
+        <v>82057252</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
+        <v>83201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,17 +855,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljusnan V om Flymyren, Vrm</t>
+          <t>Ljusnan, V om Flymyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392421.1527764776</v>
+        <v>392437</v>
       </c>
       <c r="R3" t="n">
-        <v>6688709.203302408</v>
+        <v>6688650</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,27 +889,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Funnen i kantzonen av ett nyligen upptaget hygge. Känd lokal i närheten.</t>
+          <t>Känd lokal (AP 1/5  2017), som jag inte besökt tidigare. Alla fruktkropparna inom liten yta. Troligen ett mycel.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,19 +915,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108330642</v>
+        <v>108337157</v>
       </c>
       <c r="B4" t="n">
         <v>81972</v>
@@ -972,7 +962,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,14 +974,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljusnan, V om Flymyren, Vrm</t>
+          <t>Ljusnan V om Flymyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392436.6420825614</v>
+        <v>392421.1527764776</v>
       </c>
       <c r="R4" t="n">
-        <v>6688645.299249651</v>
+        <v>6688709.203302408</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1038,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Uppföljning av tidigare känd lokal. Lokalen bedöms vara vid god status.  Exkursion med Klarälvdalens folkhögskola, Natur- och faunavård.</t>
+          <t>Funnen i kantzonen av ett nyligen upptaget hygge. Känd lokal i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,30 +1044,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Agnes Rengren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Björk, Åsa Röstell, Shoko Sato, Jonas Göransson, Amanda Sandberg, Daniel Hertz Wallin , August Oljeqvist, Agnes Rengren, Jenny NILSSON, Olavi Niemelä, Magnus Malmqvist, Johanna Klauss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2023</t>
-        </is>
-      </c>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116138308</v>
+        <v>108330642</v>
       </c>
       <c r="B5" t="n">
-        <v>83044</v>
+        <v>81972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1105,7 +1091,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1121,13 +1107,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392437</v>
+        <v>392436.6420825614</v>
       </c>
       <c r="R5" t="n">
-        <v>6688650</v>
+        <v>6688645.299249651</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1151,17 +1137,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lokalen belägen mellan vägen och älven. Nederdelen av lokalen har varit översvämmad för någon veckan sedan. Sex av fruktkropparna har tydligt påverkats av detta. Elva fuktkroppar var fräscha och fina. Enstaka granbarkborregranar.</t>
+          <t>Uppföljning av tidigare känd lokal. Lokalen bedöms vara vid god status.  Exkursion med Klarälvdalens folkhögskola, Natur- och faunavård.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,17 +1173,17 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Anton Björk, Åsa Röstell, Shoko Sato, Jonas Göransson, Amanda Sandberg, Daniel Hertz Wallin , August Oljeqvist, Agnes Rengren, Jenny NILSSON, Olavi Niemelä, Magnus Malmqvist, Johanna Klauss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Uppföljning bombmurkla 2024</t>
+          <t>Uppföljning bombmurkla 2023</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>82057252</v>
       </c>
       <c r="B3" t="n">
-        <v>83201</v>
+        <v>83208</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>82057252</v>
       </c>
       <c r="B3" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -808,14 +808,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82057252</v>
+        <v>108337157</v>
       </c>
       <c r="B3" t="n">
-        <v>83222</v>
+        <v>81972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,17 +855,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljusnan, V om Flymyren, Vrm</t>
+          <t>Ljusnan V om Flymyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392437</v>
+        <v>392421.1527764776</v>
       </c>
       <c r="R3" t="n">
-        <v>6688650</v>
+        <v>6688709.203302408</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,17 +889,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Känd lokal (AP 1/5  2017), som jag inte besökt tidigare. Alla fruktkropparna inom liten yta. Troligen ett mycel.</t>
+          <t>Funnen i kantzonen av ett nyligen upptaget hygge. Känd lokal i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,19 +925,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Agnes Rengren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Agnes Rengren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108337157</v>
+        <v>108330642</v>
       </c>
       <c r="B4" t="n">
         <v>81972</v>
@@ -962,7 +972,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,14 +984,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljusnan V om Flymyren, Vrm</t>
+          <t>Ljusnan, V om Flymyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392421.1527764776</v>
+        <v>392436.6420825614</v>
       </c>
       <c r="R4" t="n">
-        <v>6688709.203302408</v>
+        <v>6688645.299249651</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,7 +1038,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Funnen i kantzonen av ett nyligen upptaget hygge. Känd lokal i närheten.</t>
+          <t>Uppföljning av tidigare känd lokal. Lokalen bedöms vara vid god status.  Exkursion med Klarälvdalens folkhögskola, Natur- och faunavård.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,22 +1054,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anton Björk, Åsa Röstell, Shoko Sato, Jonas Göransson, Amanda Sandberg, Daniel Hertz Wallin , August Oljeqvist, Agnes Rengren, Jenny NILSSON, Olavi Niemelä, Magnus Malmqvist, Johanna Klauss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108330642</v>
+        <v>123930488</v>
       </c>
       <c r="B5" t="n">
-        <v>81972</v>
+        <v>83402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1107,13 +1121,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392436.6420825614</v>
+        <v>392436</v>
       </c>
       <c r="R5" t="n">
-        <v>6688645.299249651</v>
+        <v>6688676</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,27 +1151,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Uppföljning av tidigare känd lokal. Lokalen bedöms vara vid god status.  Exkursion med Klarälvdalens folkhögskola, Natur- och faunavård.</t>
+          <t>Känd dellokal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,17 +1177,17 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Björk, Åsa Röstell, Shoko Sato, Jonas Göransson, Amanda Sandberg, Daniel Hertz Wallin , August Oljeqvist, Agnes Rengren, Jenny NILSSON, Olavi Niemelä, Magnus Malmqvist, Johanna Klauss</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Uppföljning bombmurkla 2023</t>
+          <t>Uppföljning bombmurkla 2025</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -1070,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123930488</v>
+        <v>123930409</v>
       </c>
       <c r="B5" t="n">
         <v>83402</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Känd dellokal.</t>
+          <t>Ny dellokal. Belägen strax N om diket från Flymyren. Troligen 2 mycel.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -1070,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123930409</v>
+        <v>123930488</v>
       </c>
       <c r="B5" t="n">
         <v>83424</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ny dellokal. Belägen strax N om diket från Flymyren. Troligen 2 mycel.</t>
+          <t>Känd dellokal.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -1070,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123930488</v>
+        <v>123930409</v>
       </c>
       <c r="B5" t="n">
         <v>83424</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Känd dellokal.</t>
+          <t>Ny dellokal. Belägen strax N om diket från Flymyren. Troligen 2 mycel.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>65236498</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392436.7883871135</v>
+        <v>392437</v>
       </c>
       <c r="R2" t="n">
-        <v>6688650.251719363</v>
+        <v>6688650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +753,9 @@
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -808,19 +793,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108337157</v>
+        <v>108330642</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -843,7 +823,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,14 +835,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljusnan V om Flymyren, Vrm</t>
+          <t>Ljusnan, V om Flymyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392421.1527764776</v>
+        <v>392437</v>
       </c>
       <c r="R3" t="n">
-        <v>6688709.203302408</v>
+        <v>6688645</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,24 +872,14 @@
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Funnen i kantzonen av ett nyligen upptaget hygge. Känd lokal i närheten.</t>
+          <t>Uppföljning av tidigare känd lokal. Lokalen bedöms vara vid god status.  Exkursion med Klarälvdalens folkhögskola, Natur- och faunavård.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,31 +895,30 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Björk, Åsa Röstell, Shoko Sato, Jonas Göransson, Amanda Sandberg, Daniel Hertz Wallin , August Oljeqvist, Agnes Rengren, Jenny NILSSON, Olavi Niemelä, Magnus Malmqvist, Johanna Klauss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108330642</v>
+        <v>108337157</v>
       </c>
       <c r="B4" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -972,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,14 +953,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljusnan, V om Flymyren, Vrm</t>
+          <t>Ljusnan V om Flymyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392436.6420825614</v>
+        <v>392421</v>
       </c>
       <c r="R4" t="n">
-        <v>6688645.299249651</v>
+        <v>6688709</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,24 +990,14 @@
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Uppföljning av tidigare känd lokal. Lokalen bedöms vara vid god status.  Exkursion med Klarälvdalens folkhögskola, Natur- och faunavård.</t>
+          <t>Funnen i kantzonen av ett nyligen upptaget hygge. Känd lokal i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,35 +1013,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Agnes Rengren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Björk, Åsa Röstell, Shoko Sato, Jonas Göransson, Amanda Sandberg, Daniel Hertz Wallin , August Oljeqvist, Agnes Rengren, Jenny NILSSON, Olavi Niemelä, Magnus Malmqvist, Johanna Klauss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2023</t>
-        </is>
-      </c>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123930409</v>
+        <v>116172896</v>
       </c>
       <c r="B5" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1105,26 +1055,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljusnan, V om Flymyren, Vrm</t>
+          <t>Ljusnan, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392436</v>
+        <v>392419</v>
       </c>
       <c r="R5" t="n">
-        <v>6688676</v>
+        <v>6688615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,17 +1097,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ny dellokal. Belägen strax N om diket från Flymyren. Troligen 2 mycel.</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,17 +1118,244 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Göransson, Albin Tengius, August Oljeqvist, Edvin Johansson , Julia Lea Falk, Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116172905</v>
+      </c>
+      <c r="B6" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ljusnan, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>392419</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6688701</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas Göransson, Albin Tengius, August Oljeqvist, Edvin Johansson , Julia Lea Falk, Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123930409</v>
+      </c>
+      <c r="B7" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ljusnan, V om Flymyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>392436</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6688676</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ny dellokal. Belägen strax N om diket från Flymyren. Troligen 2 mycel.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Rolf Tidemalm</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Rolf Tidemalm</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 51288-2022 artfynd.xlsx
+++ b/artfynd/A 51288-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65236498</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108330642</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108337157</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116172896</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116172905</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,8 +1388,21 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123930409</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>